--- a/Data/HeroData.xlsx
+++ b/Data/HeroData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="11430" windowHeight="4485"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>#</t>
   </si>
@@ -43,7 +43,10 @@
     <t>int</t>
   </si>
   <si>
-    <t>List(|</t>
+    <t>List(|)</t>
+  </si>
+  <si>
+    <t>武器坐标(商店里)</t>
   </si>
   <si>
     <t>0,0|100,100|100,-100|-100,100|-100,-100</t>
@@ -992,10 +995,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="121.125" customWidth="1"/>
+    <col min="4" max="4" width="56.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:3">
@@ -1020,15 +1024,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3">
+    <row r="3" s="1" customFormat="1" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
